--- a/NetworkInvestment/results/summary.xlsx
+++ b/NetworkInvestment/results/summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jagan024\Desktop\CCG-RODDU\NetworkInvestment\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DE3544-E29B-4290-B9E4-85EF1D1399C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99C94B8-63BB-4F87-BC2E-83C5B6DB3F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -596,7 +596,10 @@
         <f>(F3-G3)/F3</f>
         <v>0.41732283464566922</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4">
+        <f>(E3-G3)/E3</f>
+        <v>-0.64444444444444449</v>
+      </c>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
@@ -631,7 +634,10 @@
         <f>(F4-G4)/F4</f>
         <v>0.41284403669724767</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="N4" s="4">
+        <f t="shared" ref="N4:N6" si="0">(E4-G4)/E4</f>
+        <v>-0.34736842105263166</v>
+      </c>
     </row>
     <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -666,7 +672,10 @@
         <f>(F5-G5)/F5</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="N5" s="4"/>
+      <c r="N5" s="4">
+        <f t="shared" si="0"/>
+        <v>-1.1267605633802817</v>
+      </c>
     </row>
     <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -701,7 +710,10 @@
         <f>(F6-G6)/F6</f>
         <v>0.64970059880239517</v>
       </c>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.62499999999999989</v>
+      </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -736,7 +748,10 @@
         <f>(126.2-109.8)/126.2</f>
         <v>0.12995245641838357</v>
       </c>
-      <c r="N7" s="4"/>
+      <c r="N7" s="4">
+        <f>(E7-109.8)/E7</f>
+        <v>-0.53351955307262577</v>
+      </c>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -771,7 +786,10 @@
         <f>(122.8-76.5)/122.8</f>
         <v>0.37703583061889251</v>
       </c>
-      <c r="N8" s="4"/>
+      <c r="N8" s="4">
+        <f>(E8-76.5)/E8</f>
+        <v>-4.5081967213114714E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -806,7 +824,10 @@
         <f>(310.1-86.9)/310.1</f>
         <v>0.71976781683327962</v>
       </c>
-      <c r="N9" s="4"/>
+      <c r="N9" s="4">
+        <f>(E9-86.9)/E9</f>
+        <v>-4.4471153846153876E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -841,7 +862,10 @@
         <f>(201.7-100.9)/201.7</f>
         <v>0.49975210708973716</v>
       </c>
-      <c r="N10" s="4"/>
+      <c r="N10" s="4">
+        <f>(E10-100.9)/E10</f>
+        <v>-0.30869001297016879</v>
+      </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -876,7 +900,10 @@
         <f>(309.7-209.2)/309.7</f>
         <v>0.32450758798837587</v>
       </c>
-      <c r="N11" s="4"/>
+      <c r="N11" s="4">
+        <f>(E11-209.2)/E11</f>
+        <v>0.5567796610169492</v>
+      </c>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -911,7 +938,10 @@
         <f>(409.9-122.4)/409.9</f>
         <v>0.70139058306904123</v>
       </c>
-      <c r="N12" s="4"/>
+      <c r="N12" s="4">
+        <f>(E12-122.4)/E12</f>
+        <v>0.71455223880597007</v>
+      </c>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -946,7 +976,10 @@
         <f>(262.8-122)/262.8</f>
         <v>0.53576864535768642</v>
       </c>
-      <c r="N13" s="4"/>
+      <c r="N13" s="4">
+        <f>(E13-122)/E13</f>
+        <v>0.67518636847710334</v>
+      </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -981,7 +1014,10 @@
         <f>(167.6-535.8)/167.6</f>
         <v>-2.1968973747016705</v>
       </c>
-      <c r="N14" s="4"/>
+      <c r="N14" s="4">
+        <f>(E14-535.8)/E14</f>
+        <v>-0.26816568047337269</v>
+      </c>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1016,7 +1052,10 @@
         <f>(645.6-98.8)/645.6</f>
         <v>0.84696406443618344</v>
       </c>
-      <c r="N15" s="4"/>
+      <c r="N15" s="4">
+        <f>(E15-98.8)/E15</f>
+        <v>0.87731280268223022</v>
+      </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1051,9 +1090,12 @@
         <f>(289.7-358)/289.7</f>
         <v>-0.23576113220573011</v>
       </c>
-      <c r="N16" s="4"/>
-    </row>
-    <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="4">
+        <f>(E16-358)/E16</f>
+        <v>0.65875512343913833</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>50</v>
       </c>
@@ -1085,8 +1127,12 @@
         <f>(255.5-574.7)/255.5</f>
         <v>-1.2493150684931509</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N17" s="2">
+        <f>(E17-574.7)/E17</f>
+        <v>0.42043162565550624</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>50</v>
       </c>
@@ -1118,8 +1164,12 @@
         <f>(294.4-175.7)/294.4</f>
         <v>0.4031929347826087</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N18" s="2">
+        <f>(E18-175.7)/E18</f>
+        <v>0.86360813538270453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>80</v>
       </c>
@@ -1151,8 +1201,12 @@
         <f>(483.6-285.8)/483.6</f>
         <v>0.4090157154673284</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N19" s="2">
+        <f>(1621.9-285.8)/1621.9</f>
+        <v>0.82378691657932057</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>80</v>
       </c>
@@ -1184,8 +1238,12 @@
         <f>(446.5-266.5)/446.5</f>
         <v>0.40313549832026874</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="2">
+        <f>(1993.3-266.5)/1993.3</f>
+        <v>0.86630211207545271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>80</v>
       </c>
@@ -1216,6 +1274,10 @@
       <c r="M21" s="2">
         <f>(512.9-324.6)/512.9</f>
         <v>0.36712809514525241</v>
+      </c>
+      <c r="N21" s="2">
+        <f>(2173-324.6)/2173</f>
+        <v>0.85062126092959045</v>
       </c>
     </row>
   </sheetData>
